--- a/artfynd/A 14097-2024 artfynd.xlsx
+++ b/artfynd/A 14097-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120257875</v>
+        <v>120257844</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473832</v>
+        <v>473793</v>
       </c>
       <c r="R2" t="n">
-        <v>7071225</v>
+        <v>7071278</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120257846</v>
+        <v>120257871</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>91023</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473799</v>
+        <v>474203</v>
       </c>
       <c r="R3" t="n">
-        <v>7071305</v>
+        <v>7071251</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>120257868</v>
       </c>
       <c r="B4" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120257865</v>
+        <v>120257883</v>
       </c>
       <c r="B5" t="n">
-        <v>90509</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473741</v>
+        <v>474185</v>
       </c>
       <c r="R5" t="n">
-        <v>7071312</v>
+        <v>7071226</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120257844</v>
+        <v>120257842</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473793</v>
+        <v>474194</v>
       </c>
       <c r="R6" t="n">
-        <v>7071278</v>
+        <v>7071238</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120257871</v>
+        <v>120257880</v>
       </c>
       <c r="B7" t="n">
-        <v>91005</v>
+        <v>90598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474203</v>
+        <v>473769</v>
       </c>
       <c r="R7" t="n">
-        <v>7071251</v>
+        <v>7071290</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120257882</v>
+        <v>120257870</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>79624</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474249</v>
+        <v>473888</v>
       </c>
       <c r="R8" t="n">
-        <v>7071213</v>
+        <v>7071263</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,11 +1373,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120257874</v>
+        <v>120257862</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>474185</v>
+        <v>473877</v>
       </c>
       <c r="R9" t="n">
-        <v>7071205</v>
+        <v>7071316</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120257863</v>
+        <v>120257845</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473881</v>
+        <v>473701</v>
       </c>
       <c r="R10" t="n">
-        <v>7071306</v>
+        <v>7071295</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,11 +1582,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120257878</v>
+        <v>120257861</v>
       </c>
       <c r="B11" t="n">
-        <v>57331</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,50 +1620,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Margitbränna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473745</v>
+        <v>473749</v>
       </c>
       <c r="R11" t="n">
-        <v>7071314</v>
+        <v>7071315</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,6 +1684,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1722,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120257859</v>
+        <v>120257853</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473696</v>
+        <v>473789</v>
       </c>
       <c r="R12" t="n">
-        <v>7071310</v>
+        <v>7071287</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,7 +1795,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,7 +1825,7 @@
         <v>120257884</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1931,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120257858</v>
+        <v>120257863</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1971,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473697</v>
+        <v>473881</v>
       </c>
       <c r="R14" t="n">
-        <v>7071295</v>
+        <v>7071306</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120257867</v>
+        <v>120257859</v>
       </c>
       <c r="B15" t="n">
-        <v>57326</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2054,16 +2047,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2078,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473747</v>
+        <v>473696</v>
       </c>
       <c r="R15" t="n">
-        <v>7071278</v>
+        <v>7071310</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,7 +2111,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2145,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120257883</v>
+        <v>120257846</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2161,21 +2154,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2185,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474185</v>
+        <v>473799</v>
       </c>
       <c r="R16" t="n">
-        <v>7071226</v>
+        <v>7071305</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2221,11 +2214,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2252,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120257866</v>
+        <v>120257885</v>
       </c>
       <c r="B17" t="n">
-        <v>57326</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2268,21 +2256,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2292,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473843</v>
+        <v>473867</v>
       </c>
       <c r="R17" t="n">
-        <v>7071272</v>
+        <v>7071321</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2328,11 +2316,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2359,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120257854</v>
+        <v>120257876</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2375,21 +2358,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2399,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473715</v>
+        <v>473697</v>
       </c>
       <c r="R18" t="n">
-        <v>7071284</v>
+        <v>7071274</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2435,11 +2418,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2466,10 +2444,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120257886</v>
+        <v>120257866</v>
       </c>
       <c r="B19" t="n">
-        <v>86878</v>
+        <v>57336</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2482,21 +2460,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2506,10 +2484,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473784</v>
+        <v>473843</v>
       </c>
       <c r="R19" t="n">
-        <v>7071287</v>
+        <v>7071272</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2542,6 +2520,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2568,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120257876</v>
+        <v>120257852</v>
       </c>
       <c r="B20" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2584,21 +2567,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2608,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473697</v>
+        <v>473757</v>
       </c>
       <c r="R20" t="n">
-        <v>7071274</v>
+        <v>7071281</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2644,6 +2627,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2670,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120257845</v>
+        <v>120257867</v>
       </c>
       <c r="B21" t="n">
-        <v>90562</v>
+        <v>57336</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2686,21 +2674,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2710,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473701</v>
+        <v>473747</v>
       </c>
       <c r="R21" t="n">
-        <v>7071295</v>
+        <v>7071278</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2746,6 +2734,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2772,10 +2765,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120257861</v>
+        <v>120257849</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2812,10 +2805,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473749</v>
+        <v>474289</v>
       </c>
       <c r="R22" t="n">
-        <v>7071315</v>
+        <v>7071246</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2879,10 +2872,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120257885</v>
+        <v>120257854</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2895,21 +2888,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2919,10 +2912,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473867</v>
+        <v>473715</v>
       </c>
       <c r="R23" t="n">
-        <v>7071321</v>
+        <v>7071284</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2955,6 +2948,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2981,10 +2979,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120257881</v>
+        <v>120257877</v>
       </c>
       <c r="B24" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2997,21 +2995,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3021,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473819</v>
+        <v>473888</v>
       </c>
       <c r="R24" t="n">
-        <v>7071302</v>
+        <v>7071263</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3086,7 +3084,7 @@
         <v>120257851</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3193,7 +3191,7 @@
         <v>120257860</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3297,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120257877</v>
+        <v>120257856</v>
       </c>
       <c r="B27" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3313,21 +3311,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3337,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473888</v>
+        <v>473708</v>
       </c>
       <c r="R27" t="n">
-        <v>7071263</v>
+        <v>7071283</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3373,6 +3371,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3399,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120257842</v>
+        <v>120257875</v>
       </c>
       <c r="B28" t="n">
-        <v>90562</v>
+        <v>79623</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3415,21 +3418,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3439,10 +3442,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>474194</v>
+        <v>473832</v>
       </c>
       <c r="R28" t="n">
-        <v>7071238</v>
+        <v>7071225</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3501,10 +3504,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120257856</v>
+        <v>120257865</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>90527</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3517,21 +3520,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3541,10 +3544,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473708</v>
+        <v>473741</v>
       </c>
       <c r="R29" t="n">
-        <v>7071283</v>
+        <v>7071312</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3577,11 +3580,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3608,10 +3606,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120257880</v>
+        <v>120257878</v>
       </c>
       <c r="B30" t="n">
-        <v>90580</v>
+        <v>57341</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3620,38 +3618,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100110</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Margitbränna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473769</v>
+        <v>473745</v>
       </c>
       <c r="R30" t="n">
-        <v>7071290</v>
+        <v>7071314</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3710,10 +3720,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120257849</v>
+        <v>120257881</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
+        <v>90598</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3726,21 +3736,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3750,10 +3760,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474289</v>
+        <v>473819</v>
       </c>
       <c r="R31" t="n">
-        <v>7071246</v>
+        <v>7071302</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3786,11 +3796,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3817,10 +3822,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120257862</v>
+        <v>120257874</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3833,21 +3838,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3857,10 +3862,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473877</v>
+        <v>474185</v>
       </c>
       <c r="R32" t="n">
-        <v>7071316</v>
+        <v>7071205</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3893,11 +3898,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3924,10 +3924,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120257870</v>
+        <v>120257882</v>
       </c>
       <c r="B33" t="n">
-        <v>79608</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3940,21 +3940,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473888</v>
+        <v>474249</v>
       </c>
       <c r="R33" t="n">
-        <v>7071263</v>
+        <v>7071213</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4000,6 +4000,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4026,10 +4031,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120257853</v>
+        <v>120257886</v>
       </c>
       <c r="B34" t="n">
-        <v>57310</v>
+        <v>86895</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4042,21 +4047,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4066,7 +4071,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473789</v>
+        <v>473784</v>
       </c>
       <c r="R34" t="n">
         <v>7071287</v>
@@ -4102,11 +4107,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4133,10 +4133,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120257852</v>
+        <v>120257858</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473757</v>
+        <v>473697</v>
       </c>
       <c r="R35" t="n">
-        <v>7071281</v>
+        <v>7071295</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 14097-2024 artfynd.xlsx
+++ b/artfynd/A 14097-2024 artfynd.xlsx
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120257883</v>
+        <v>120257842</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474185</v>
+        <v>474194</v>
       </c>
       <c r="R5" t="n">
-        <v>7071226</v>
+        <v>7071238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120257842</v>
+        <v>120257883</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474194</v>
+        <v>474185</v>
       </c>
       <c r="R6" t="n">
-        <v>7071238</v>
+        <v>7071226</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120257884</v>
+        <v>120257863</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473879</v>
+        <v>473881</v>
       </c>
       <c r="R13" t="n">
-        <v>7071280</v>
+        <v>7071306</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,6 +1898,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,7 +1929,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120257863</v>
+        <v>120257859</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1964,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473881</v>
+        <v>473696</v>
       </c>
       <c r="R14" t="n">
-        <v>7071306</v>
+        <v>7071310</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,7 +2009,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2031,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120257859</v>
+        <v>120257884</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,21 +2052,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2071,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473696</v>
+        <v>473879</v>
       </c>
       <c r="R15" t="n">
-        <v>7071310</v>
+        <v>7071280</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,11 +2112,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2872,10 +2872,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120257854</v>
+        <v>120257877</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2888,21 +2888,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473715</v>
+        <v>473888</v>
       </c>
       <c r="R23" t="n">
-        <v>7071284</v>
+        <v>7071263</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,11 +2948,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2979,10 +2974,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120257877</v>
+        <v>120257854</v>
       </c>
       <c r="B24" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2995,21 +2990,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3019,10 +3014,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473888</v>
+        <v>473715</v>
       </c>
       <c r="R24" t="n">
-        <v>7071263</v>
+        <v>7071284</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3055,6 +3050,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 14097-2024 artfynd.xlsx
+++ b/artfynd/A 14097-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120257844</v>
+        <v>120257875</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473793</v>
+        <v>473832</v>
       </c>
       <c r="R2" t="n">
-        <v>7071278</v>
+        <v>7071225</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120257871</v>
+        <v>120257883</v>
       </c>
       <c r="B3" t="n">
-        <v>91023</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474203</v>
+        <v>474185</v>
       </c>
       <c r="R3" t="n">
-        <v>7071251</v>
+        <v>7071226</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120257868</v>
+        <v>120257876</v>
       </c>
       <c r="B4" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473985</v>
+        <v>473697</v>
       </c>
       <c r="R4" t="n">
-        <v>7071183</v>
+        <v>7071274</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120257842</v>
+        <v>120257854</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474194</v>
+        <v>473715</v>
       </c>
       <c r="R5" t="n">
-        <v>7071238</v>
+        <v>7071284</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120257883</v>
+        <v>120257863</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>474185</v>
+        <v>473881</v>
       </c>
       <c r="R6" t="n">
-        <v>7071226</v>
+        <v>7071306</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120257880</v>
+        <v>120257871</v>
       </c>
       <c r="B7" t="n">
-        <v>90598</v>
+        <v>91023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473769</v>
+        <v>474203</v>
       </c>
       <c r="R7" t="n">
-        <v>7071290</v>
+        <v>7071251</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120257870</v>
+        <v>120257882</v>
       </c>
       <c r="B8" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473888</v>
+        <v>474249</v>
       </c>
       <c r="R8" t="n">
-        <v>7071263</v>
+        <v>7071213</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,6 +1378,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120257862</v>
+        <v>120257865</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>90527</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473877</v>
+        <v>473741</v>
       </c>
       <c r="R9" t="n">
-        <v>7071316</v>
+        <v>7071312</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,11 +1485,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,7 +1511,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120257845</v>
+        <v>120257844</v>
       </c>
       <c r="B10" t="n">
         <v>90580</v>
@@ -1546,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473701</v>
+        <v>473793</v>
       </c>
       <c r="R10" t="n">
-        <v>7071295</v>
+        <v>7071278</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120257861</v>
+        <v>120257845</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473749</v>
+        <v>473701</v>
       </c>
       <c r="R11" t="n">
-        <v>7071315</v>
+        <v>7071295</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,11 +1689,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120257853</v>
+        <v>120257885</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473789</v>
+        <v>473867</v>
       </c>
       <c r="R12" t="n">
-        <v>7071287</v>
+        <v>7071321</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,11 +1791,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120257863</v>
+        <v>120257870</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473881</v>
+        <v>473888</v>
       </c>
       <c r="R13" t="n">
-        <v>7071306</v>
+        <v>7071263</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,11 +1893,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,7 +1919,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120257859</v>
+        <v>120257860</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1969,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473696</v>
+        <v>473734</v>
       </c>
       <c r="R14" t="n">
-        <v>7071310</v>
+        <v>7071302</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2009,7 +1999,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2138,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120257846</v>
+        <v>120257851</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2154,21 +2144,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473799</v>
+        <v>473805</v>
       </c>
       <c r="R16" t="n">
-        <v>7071305</v>
+        <v>7071239</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,6 +2204,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2240,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120257885</v>
+        <v>120257856</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2256,21 +2251,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2280,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473867</v>
+        <v>473708</v>
       </c>
       <c r="R17" t="n">
-        <v>7071321</v>
+        <v>7071283</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,6 +2311,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120257876</v>
+        <v>120257880</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>90598</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2358,21 +2358,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2382,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473697</v>
+        <v>473769</v>
       </c>
       <c r="R18" t="n">
-        <v>7071274</v>
+        <v>7071290</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2444,10 +2444,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120257866</v>
+        <v>120257858</v>
       </c>
       <c r="B19" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473843</v>
+        <v>473697</v>
       </c>
       <c r="R19" t="n">
-        <v>7071272</v>
+        <v>7071295</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2551,7 +2551,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120257852</v>
+        <v>120257853</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473757</v>
+        <v>473789</v>
       </c>
       <c r="R20" t="n">
-        <v>7071281</v>
+        <v>7071287</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2658,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120257867</v>
+        <v>120257859</v>
       </c>
       <c r="B21" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2674,16 +2674,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473747</v>
+        <v>473696</v>
       </c>
       <c r="R21" t="n">
-        <v>7071278</v>
+        <v>7071310</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2765,10 +2765,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120257849</v>
+        <v>120257866</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2781,16 +2781,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2805,10 +2805,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474289</v>
+        <v>473843</v>
       </c>
       <c r="R22" t="n">
-        <v>7071246</v>
+        <v>7071272</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2872,10 +2872,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120257877</v>
+        <v>120257867</v>
       </c>
       <c r="B23" t="n">
-        <v>79623</v>
+        <v>57336</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2888,21 +2888,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473888</v>
+        <v>473747</v>
       </c>
       <c r="R23" t="n">
-        <v>7071263</v>
+        <v>7071278</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,6 +2948,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2974,7 +2979,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120257854</v>
+        <v>120257849</v>
       </c>
       <c r="B24" t="n">
         <v>57320</v>
@@ -3014,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473715</v>
+        <v>474289</v>
       </c>
       <c r="R24" t="n">
-        <v>7071284</v>
+        <v>7071246</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,10 +3086,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120257851</v>
+        <v>120257881</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3097,21 +3102,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3121,10 +3126,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473805</v>
+        <v>473819</v>
       </c>
       <c r="R25" t="n">
-        <v>7071239</v>
+        <v>7071302</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3157,11 +3162,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3188,7 +3188,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120257860</v>
+        <v>120257852</v>
       </c>
       <c r="B26" t="n">
         <v>57320</v>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473734</v>
+        <v>473757</v>
       </c>
       <c r="R26" t="n">
-        <v>7071302</v>
+        <v>7071281</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3295,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120257856</v>
+        <v>120257877</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3311,21 +3311,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473708</v>
+        <v>473888</v>
       </c>
       <c r="R27" t="n">
-        <v>7071283</v>
+        <v>7071263</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3371,11 +3371,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3402,10 +3397,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120257875</v>
+        <v>120257878</v>
       </c>
       <c r="B28" t="n">
-        <v>79623</v>
+        <v>57341</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3414,38 +3409,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100110</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Margitbränna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473832</v>
+        <v>473745</v>
       </c>
       <c r="R28" t="n">
-        <v>7071225</v>
+        <v>7071314</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3504,10 +3511,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120257865</v>
+        <v>120257874</v>
       </c>
       <c r="B29" t="n">
-        <v>90527</v>
+        <v>79623</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3520,21 +3527,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3544,10 +3551,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473741</v>
+        <v>474185</v>
       </c>
       <c r="R29" t="n">
-        <v>7071312</v>
+        <v>7071205</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3606,10 +3613,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120257878</v>
+        <v>120257861</v>
       </c>
       <c r="B30" t="n">
-        <v>57341</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3618,50 +3625,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Margitbränna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473745</v>
+        <v>473749</v>
       </c>
       <c r="R30" t="n">
-        <v>7071314</v>
+        <v>7071315</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3694,6 +3689,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3720,10 +3720,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120257881</v>
+        <v>120257842</v>
       </c>
       <c r="B31" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3736,21 +3736,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473819</v>
+        <v>474194</v>
       </c>
       <c r="R31" t="n">
-        <v>7071302</v>
+        <v>7071238</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120257874</v>
+        <v>120257868</v>
       </c>
       <c r="B32" t="n">
-        <v>79623</v>
+        <v>57336</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3838,21 +3838,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3862,10 +3862,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474185</v>
+        <v>473985</v>
       </c>
       <c r="R32" t="n">
-        <v>7071205</v>
+        <v>7071183</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3898,6 +3898,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3924,10 +3929,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120257882</v>
+        <v>120257862</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3940,21 +3945,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3964,10 +3969,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>474249</v>
+        <v>473877</v>
       </c>
       <c r="R33" t="n">
-        <v>7071213</v>
+        <v>7071316</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4004,7 +4009,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4031,10 +4036,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120257886</v>
+        <v>120257846</v>
       </c>
       <c r="B34" t="n">
-        <v>86895</v>
+        <v>90580</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4047,21 +4052,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4071,10 +4076,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473784</v>
+        <v>473799</v>
       </c>
       <c r="R34" t="n">
-        <v>7071287</v>
+        <v>7071305</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4133,10 +4138,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120257858</v>
+        <v>120257886</v>
       </c>
       <c r="B35" t="n">
-        <v>57320</v>
+        <v>86895</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4149,21 +4154,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4173,10 +4178,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473697</v>
+        <v>473784</v>
       </c>
       <c r="R35" t="n">
-        <v>7071295</v>
+        <v>7071287</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4209,11 +4214,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 14097-2024 artfynd.xlsx
+++ b/artfynd/A 14097-2024 artfynd.xlsx
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120257854</v>
+        <v>120257882</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473715</v>
+        <v>474249</v>
       </c>
       <c r="R5" t="n">
-        <v>7071284</v>
+        <v>7071213</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120257863</v>
+        <v>120257854</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473881</v>
+        <v>473715</v>
       </c>
       <c r="R6" t="n">
-        <v>7071306</v>
+        <v>7071284</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120257871</v>
+        <v>120257863</v>
       </c>
       <c r="B7" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>474203</v>
+        <v>473881</v>
       </c>
       <c r="R7" t="n">
-        <v>7071251</v>
+        <v>7071306</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120257882</v>
+        <v>120257871</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>91023</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,25 +1319,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474249</v>
+        <v>474203</v>
       </c>
       <c r="R8" t="n">
-        <v>7071213</v>
+        <v>7071251</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,11 +1383,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 14097-2024 artfynd.xlsx
+++ b/artfynd/A 14097-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120257875</v>
+        <v>120257880</v>
       </c>
       <c r="B2" t="n">
-        <v>79623</v>
+        <v>90598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473832</v>
+        <v>473769</v>
       </c>
       <c r="R2" t="n">
-        <v>7071225</v>
+        <v>7071290</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120257883</v>
+        <v>120257853</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474185</v>
+        <v>473789</v>
       </c>
       <c r="R3" t="n">
-        <v>7071226</v>
+        <v>7071287</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120257876</v>
+        <v>120257875</v>
       </c>
       <c r="B4" t="n">
         <v>79623</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473697</v>
+        <v>473832</v>
       </c>
       <c r="R4" t="n">
-        <v>7071274</v>
+        <v>7071225</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120257882</v>
+        <v>120257844</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474249</v>
+        <v>473793</v>
       </c>
       <c r="R5" t="n">
-        <v>7071213</v>
+        <v>7071278</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120257854</v>
+        <v>120257845</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473715</v>
+        <v>473701</v>
       </c>
       <c r="R6" t="n">
-        <v>7071284</v>
+        <v>7071295</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120257863</v>
+        <v>120257884</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473881</v>
+        <v>473879</v>
       </c>
       <c r="R7" t="n">
-        <v>7071306</v>
+        <v>7071280</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120257871</v>
+        <v>120257885</v>
       </c>
       <c r="B8" t="n">
-        <v>91023</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>474203</v>
+        <v>473867</v>
       </c>
       <c r="R8" t="n">
-        <v>7071251</v>
+        <v>7071321</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120257865</v>
+        <v>120257870</v>
       </c>
       <c r="B9" t="n">
-        <v>90527</v>
+        <v>79624</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>112</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473741</v>
+        <v>473888</v>
       </c>
       <c r="R9" t="n">
-        <v>7071312</v>
+        <v>7071263</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120257844</v>
+        <v>120257866</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473793</v>
+        <v>473843</v>
       </c>
       <c r="R10" t="n">
-        <v>7071278</v>
+        <v>7071272</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,6 +1572,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120257845</v>
+        <v>120257851</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473701</v>
+        <v>473805</v>
       </c>
       <c r="R11" t="n">
-        <v>7071295</v>
+        <v>7071239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,6 +1679,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120257885</v>
+        <v>120257842</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473867</v>
+        <v>474194</v>
       </c>
       <c r="R12" t="n">
-        <v>7071321</v>
+        <v>7071238</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120257870</v>
+        <v>120257846</v>
       </c>
       <c r="B13" t="n">
-        <v>79624</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473888</v>
+        <v>473799</v>
       </c>
       <c r="R13" t="n">
-        <v>7071263</v>
+        <v>7071305</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120257860</v>
+        <v>120257882</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473734</v>
+        <v>474249</v>
       </c>
       <c r="R14" t="n">
-        <v>7071302</v>
+        <v>7071213</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,7 +1994,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2026,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120257884</v>
+        <v>120257861</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473879</v>
+        <v>473749</v>
       </c>
       <c r="R15" t="n">
-        <v>7071280</v>
+        <v>7071315</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,6 +2097,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,7 +2128,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120257851</v>
+        <v>120257860</v>
       </c>
       <c r="B16" t="n">
         <v>57320</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473805</v>
+        <v>473734</v>
       </c>
       <c r="R16" t="n">
-        <v>7071239</v>
+        <v>7071302</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120257856</v>
+        <v>120257883</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2251,21 +2251,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473708</v>
+        <v>474185</v>
       </c>
       <c r="R17" t="n">
-        <v>7071283</v>
+        <v>7071226</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2342,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120257880</v>
+        <v>120257863</v>
       </c>
       <c r="B18" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2358,21 +2358,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2382,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473769</v>
+        <v>473881</v>
       </c>
       <c r="R18" t="n">
-        <v>7071290</v>
+        <v>7071306</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,6 +2418,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2444,7 +2449,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120257858</v>
+        <v>120257862</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2484,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473697</v>
+        <v>473877</v>
       </c>
       <c r="R19" t="n">
-        <v>7071295</v>
+        <v>7071316</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2524,7 +2529,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2551,7 +2556,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120257853</v>
+        <v>120257849</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2591,10 +2596,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473789</v>
+        <v>474289</v>
       </c>
       <c r="R20" t="n">
-        <v>7071287</v>
+        <v>7071246</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2631,7 +2636,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2658,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120257859</v>
+        <v>120257865</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>90527</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2674,21 +2679,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2698,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473696</v>
+        <v>473741</v>
       </c>
       <c r="R21" t="n">
-        <v>7071310</v>
+        <v>7071312</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,11 +2739,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2765,10 +2765,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120257866</v>
+        <v>120257881</v>
       </c>
       <c r="B22" t="n">
-        <v>57336</v>
+        <v>90598</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2781,21 +2781,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2805,10 +2805,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473843</v>
+        <v>473819</v>
       </c>
       <c r="R22" t="n">
-        <v>7071272</v>
+        <v>7071302</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2841,11 +2841,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2872,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120257867</v>
+        <v>120257886</v>
       </c>
       <c r="B23" t="n">
-        <v>57336</v>
+        <v>86895</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2888,21 +2883,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2912,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473747</v>
+        <v>473784</v>
       </c>
       <c r="R23" t="n">
-        <v>7071278</v>
+        <v>7071287</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,11 +2943,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2979,10 +2969,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120257849</v>
+        <v>120257868</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2995,16 +2985,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3019,10 +3009,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>474289</v>
+        <v>473985</v>
       </c>
       <c r="R24" t="n">
-        <v>7071246</v>
+        <v>7071183</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3059,7 +3049,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3086,10 +3076,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120257881</v>
+        <v>120257871</v>
       </c>
       <c r="B25" t="n">
-        <v>90598</v>
+        <v>91023</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3098,25 +3088,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3126,10 +3116,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473819</v>
+        <v>474203</v>
       </c>
       <c r="R25" t="n">
-        <v>7071302</v>
+        <v>7071251</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3188,10 +3178,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120257852</v>
+        <v>120257867</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3204,16 +3194,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3228,10 +3218,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473757</v>
+        <v>473747</v>
       </c>
       <c r="R26" t="n">
-        <v>7071281</v>
+        <v>7071278</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3268,7 +3258,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3295,10 +3285,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120257877</v>
+        <v>120257852</v>
       </c>
       <c r="B27" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3311,21 +3301,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3335,10 +3325,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473888</v>
+        <v>473757</v>
       </c>
       <c r="R27" t="n">
-        <v>7071263</v>
+        <v>7071281</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3371,6 +3361,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3397,10 +3392,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120257878</v>
+        <v>120257859</v>
       </c>
       <c r="B28" t="n">
-        <v>57341</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3409,50 +3404,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Margitbränna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473745</v>
+        <v>473696</v>
       </c>
       <c r="R28" t="n">
-        <v>7071314</v>
+        <v>7071310</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3485,6 +3468,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3511,7 +3499,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120257874</v>
+        <v>120257877</v>
       </c>
       <c r="B29" t="n">
         <v>79623</v>
@@ -3551,10 +3539,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474185</v>
+        <v>473888</v>
       </c>
       <c r="R29" t="n">
-        <v>7071205</v>
+        <v>7071263</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3613,7 +3601,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120257861</v>
+        <v>120257858</v>
       </c>
       <c r="B30" t="n">
         <v>57320</v>
@@ -3653,10 +3641,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473749</v>
+        <v>473697</v>
       </c>
       <c r="R30" t="n">
-        <v>7071315</v>
+        <v>7071295</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3720,10 +3708,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120257842</v>
+        <v>120257878</v>
       </c>
       <c r="B31" t="n">
-        <v>90580</v>
+        <v>57341</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3732,38 +3720,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100110</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Margitbränna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>474194</v>
+        <v>473745</v>
       </c>
       <c r="R31" t="n">
-        <v>7071238</v>
+        <v>7071314</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3822,10 +3822,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120257868</v>
+        <v>120257874</v>
       </c>
       <c r="B32" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3838,21 +3838,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3862,10 +3862,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473985</v>
+        <v>474185</v>
       </c>
       <c r="R32" t="n">
-        <v>7071183</v>
+        <v>7071205</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3898,11 +3898,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3929,7 +3924,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120257862</v>
+        <v>120257854</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -3969,10 +3964,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473877</v>
+        <v>473715</v>
       </c>
       <c r="R33" t="n">
-        <v>7071316</v>
+        <v>7071284</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4009,7 +4004,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4036,10 +4031,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120257846</v>
+        <v>120257856</v>
       </c>
       <c r="B34" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4052,21 +4047,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4076,10 +4071,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473799</v>
+        <v>473708</v>
       </c>
       <c r="R34" t="n">
-        <v>7071305</v>
+        <v>7071283</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4112,6 +4107,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4138,10 +4138,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120257886</v>
+        <v>120257876</v>
       </c>
       <c r="B35" t="n">
-        <v>86895</v>
+        <v>79623</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4154,21 +4154,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473784</v>
+        <v>473697</v>
       </c>
       <c r="R35" t="n">
-        <v>7071287</v>
+        <v>7071274</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 14097-2024 artfynd.xlsx
+++ b/artfynd/A 14097-2024 artfynd.xlsx
@@ -2663,10 +2663,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120257865</v>
+        <v>120257881</v>
       </c>
       <c r="B21" t="n">
-        <v>90527</v>
+        <v>90598</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2679,21 +2679,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473741</v>
+        <v>473819</v>
       </c>
       <c r="R21" t="n">
-        <v>7071312</v>
+        <v>7071302</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,10 +2765,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120257881</v>
+        <v>120257865</v>
       </c>
       <c r="B22" t="n">
-        <v>90598</v>
+        <v>90527</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2781,21 +2781,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2805,10 +2805,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473819</v>
+        <v>473741</v>
       </c>
       <c r="R22" t="n">
-        <v>7071302</v>
+        <v>7071312</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 14097-2024 artfynd.xlsx
+++ b/artfynd/A 14097-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120257880</v>
+        <v>120257885</v>
       </c>
       <c r="B2" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473769</v>
+        <v>473867</v>
       </c>
       <c r="R2" t="n">
-        <v>7071290</v>
+        <v>7071321</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120257853</v>
+        <v>120257856</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473789</v>
+        <v>473708</v>
       </c>
       <c r="R3" t="n">
-        <v>7071287</v>
+        <v>7071283</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120257875</v>
+        <v>120257849</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473832</v>
+        <v>474289</v>
       </c>
       <c r="R4" t="n">
-        <v>7071225</v>
+        <v>7071246</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120257845</v>
+        <v>120257875</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473701</v>
+        <v>473832</v>
       </c>
       <c r="R6" t="n">
-        <v>7071295</v>
+        <v>7071225</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120257884</v>
+        <v>120257886</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>86895</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473879</v>
+        <v>473784</v>
       </c>
       <c r="R7" t="n">
-        <v>7071280</v>
+        <v>7071287</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120257885</v>
+        <v>120257881</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473867</v>
+        <v>473819</v>
       </c>
       <c r="R8" t="n">
-        <v>7071321</v>
+        <v>7071302</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120257870</v>
+        <v>120257862</v>
       </c>
       <c r="B9" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473888</v>
+        <v>473877</v>
       </c>
       <c r="R9" t="n">
-        <v>7071263</v>
+        <v>7071316</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1470,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120257866</v>
+        <v>120257880</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
+        <v>90598</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1512,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473843</v>
+        <v>473769</v>
       </c>
       <c r="R10" t="n">
-        <v>7071272</v>
+        <v>7071290</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,11 +1582,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120257851</v>
+        <v>120257870</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473805</v>
+        <v>473888</v>
       </c>
       <c r="R11" t="n">
-        <v>7071239</v>
+        <v>7071263</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1679,11 +1684,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120257842</v>
+        <v>120257884</v>
       </c>
       <c r="B12" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>474194</v>
+        <v>473879</v>
       </c>
       <c r="R12" t="n">
-        <v>7071238</v>
+        <v>7071280</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120257846</v>
+        <v>120257868</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>57336</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473799</v>
+        <v>473985</v>
       </c>
       <c r="R13" t="n">
-        <v>7071305</v>
+        <v>7071183</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,6 +1888,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120257882</v>
+        <v>120257874</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474249</v>
+        <v>474185</v>
       </c>
       <c r="R14" t="n">
-        <v>7071213</v>
+        <v>7071205</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1990,11 +1995,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120257861</v>
+        <v>120257882</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473749</v>
+        <v>474249</v>
       </c>
       <c r="R15" t="n">
-        <v>7071315</v>
+        <v>7071213</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120257860</v>
+        <v>120257876</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2144,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473734</v>
+        <v>473697</v>
       </c>
       <c r="R16" t="n">
-        <v>7071302</v>
+        <v>7071274</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2204,11 +2204,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120257883</v>
+        <v>120257866</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2251,21 +2246,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2275,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>474185</v>
+        <v>473843</v>
       </c>
       <c r="R17" t="n">
-        <v>7071226</v>
+        <v>7071272</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2315,7 +2310,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2342,7 +2337,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120257863</v>
+        <v>120257858</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2382,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473881</v>
+        <v>473697</v>
       </c>
       <c r="R18" t="n">
-        <v>7071306</v>
+        <v>7071295</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2449,7 +2444,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120257862</v>
+        <v>120257851</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2489,10 +2484,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473877</v>
+        <v>473805</v>
       </c>
       <c r="R19" t="n">
-        <v>7071316</v>
+        <v>7071239</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,7 +2524,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2556,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120257849</v>
+        <v>120257883</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2572,21 +2567,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2596,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474289</v>
+        <v>474185</v>
       </c>
       <c r="R20" t="n">
-        <v>7071246</v>
+        <v>7071226</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2636,7 +2631,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2663,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120257881</v>
+        <v>120257877</v>
       </c>
       <c r="B21" t="n">
-        <v>90598</v>
+        <v>79623</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2679,21 +2674,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2703,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473819</v>
+        <v>473888</v>
       </c>
       <c r="R21" t="n">
-        <v>7071302</v>
+        <v>7071263</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2765,10 +2760,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120257865</v>
+        <v>120257878</v>
       </c>
       <c r="B22" t="n">
-        <v>90527</v>
+        <v>57341</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2777,38 +2772,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>112</v>
+        <v>100110</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Margitbränna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473741</v>
+        <v>473745</v>
       </c>
       <c r="R22" t="n">
-        <v>7071312</v>
+        <v>7071314</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2867,10 +2874,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120257886</v>
+        <v>120257860</v>
       </c>
       <c r="B23" t="n">
-        <v>86895</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2883,21 +2890,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2907,10 +2914,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473784</v>
+        <v>473734</v>
       </c>
       <c r="R23" t="n">
-        <v>7071287</v>
+        <v>7071302</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2943,6 +2950,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2969,7 +2981,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120257868</v>
+        <v>120257867</v>
       </c>
       <c r="B24" t="n">
         <v>57336</v>
@@ -3009,10 +3021,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473985</v>
+        <v>473747</v>
       </c>
       <c r="R24" t="n">
-        <v>7071183</v>
+        <v>7071278</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3076,10 +3088,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120257871</v>
+        <v>120257863</v>
       </c>
       <c r="B25" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3088,25 +3100,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3116,10 +3128,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474203</v>
+        <v>473881</v>
       </c>
       <c r="R25" t="n">
-        <v>7071251</v>
+        <v>7071306</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,6 +3164,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3178,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120257867</v>
+        <v>120257865</v>
       </c>
       <c r="B26" t="n">
-        <v>57336</v>
+        <v>90527</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3194,21 +3211,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3218,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473747</v>
+        <v>473741</v>
       </c>
       <c r="R26" t="n">
-        <v>7071278</v>
+        <v>7071312</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3254,11 +3271,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3285,7 +3297,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120257852</v>
+        <v>120257853</v>
       </c>
       <c r="B27" t="n">
         <v>57320</v>
@@ -3325,10 +3337,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473757</v>
+        <v>473789</v>
       </c>
       <c r="R27" t="n">
-        <v>7071281</v>
+        <v>7071287</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3365,7 +3377,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3392,10 +3404,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120257859</v>
+        <v>120257846</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3408,21 +3420,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3432,10 +3444,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473696</v>
+        <v>473799</v>
       </c>
       <c r="R28" t="n">
-        <v>7071310</v>
+        <v>7071305</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3468,11 +3480,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3499,10 +3506,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120257877</v>
+        <v>120257842</v>
       </c>
       <c r="B29" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3515,21 +3522,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3539,10 +3546,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473888</v>
+        <v>474194</v>
       </c>
       <c r="R29" t="n">
-        <v>7071263</v>
+        <v>7071238</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3601,7 +3608,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120257858</v>
+        <v>120257859</v>
       </c>
       <c r="B30" t="n">
         <v>57320</v>
@@ -3641,10 +3648,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473697</v>
+        <v>473696</v>
       </c>
       <c r="R30" t="n">
-        <v>7071295</v>
+        <v>7071310</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3681,7 +3688,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3708,10 +3715,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120257878</v>
+        <v>120257861</v>
       </c>
       <c r="B31" t="n">
-        <v>57341</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3720,50 +3727,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Margitbränna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473745</v>
+        <v>473749</v>
       </c>
       <c r="R31" t="n">
-        <v>7071314</v>
+        <v>7071315</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3796,6 +3791,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3822,10 +3822,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120257874</v>
+        <v>120257854</v>
       </c>
       <c r="B32" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3838,21 +3838,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3862,10 +3862,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>474185</v>
+        <v>473715</v>
       </c>
       <c r="R32" t="n">
-        <v>7071205</v>
+        <v>7071284</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3898,6 +3898,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3924,10 +3929,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120257854</v>
+        <v>120257845</v>
       </c>
       <c r="B33" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3940,21 +3945,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3964,10 +3969,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473715</v>
+        <v>473701</v>
       </c>
       <c r="R33" t="n">
-        <v>7071284</v>
+        <v>7071295</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4000,11 +4005,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4031,10 +4031,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120257856</v>
+        <v>120257871</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4043,25 +4043,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473708</v>
+        <v>474203</v>
       </c>
       <c r="R34" t="n">
-        <v>7071283</v>
+        <v>7071251</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4107,11 +4107,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4138,10 +4133,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120257876</v>
+        <v>120257852</v>
       </c>
       <c r="B35" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4154,21 +4149,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4178,10 +4173,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473697</v>
+        <v>473757</v>
       </c>
       <c r="R35" t="n">
-        <v>7071274</v>
+        <v>7071281</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4214,6 +4209,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 14097-2024 artfynd.xlsx
+++ b/artfynd/A 14097-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120257885</v>
+        <v>120257842</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473867</v>
+        <v>474194</v>
       </c>
       <c r="R2" t="n">
-        <v>7071321</v>
+        <v>7071238</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120257856</v>
+        <v>120257881</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473708</v>
+        <v>473819</v>
       </c>
       <c r="R3" t="n">
-        <v>7071283</v>
+        <v>7071302</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120257849</v>
+        <v>120257851</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474289</v>
+        <v>473805</v>
       </c>
       <c r="R4" t="n">
-        <v>7071246</v>
+        <v>7071239</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120257844</v>
+        <v>120257877</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473793</v>
+        <v>473888</v>
       </c>
       <c r="R5" t="n">
-        <v>7071278</v>
+        <v>7071263</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120257875</v>
+        <v>120257854</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473832</v>
+        <v>473715</v>
       </c>
       <c r="R6" t="n">
-        <v>7071225</v>
+        <v>7071284</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120257886</v>
+        <v>120257845</v>
       </c>
       <c r="B7" t="n">
-        <v>86895</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473784</v>
+        <v>473701</v>
       </c>
       <c r="R7" t="n">
-        <v>7071287</v>
+        <v>7071295</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120257881</v>
+        <v>120257844</v>
       </c>
       <c r="B8" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473819</v>
+        <v>473793</v>
       </c>
       <c r="R8" t="n">
-        <v>7071302</v>
+        <v>7071278</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120257880</v>
+        <v>120257885</v>
       </c>
       <c r="B10" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473769</v>
+        <v>473867</v>
       </c>
       <c r="R10" t="n">
-        <v>7071290</v>
+        <v>7071321</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120257870</v>
+        <v>120257878</v>
       </c>
       <c r="B11" t="n">
-        <v>79624</v>
+        <v>57341</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,38 +1620,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>100110</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Margitbränna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473888</v>
+        <v>473745</v>
       </c>
       <c r="R11" t="n">
-        <v>7071263</v>
+        <v>7071314</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1722,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120257884</v>
+        <v>120257856</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1738,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1762,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473879</v>
+        <v>473708</v>
       </c>
       <c r="R12" t="n">
-        <v>7071280</v>
+        <v>7071283</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1786,6 +1798,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,10 +1829,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120257868</v>
+        <v>120257875</v>
       </c>
       <c r="B13" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1845,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1869,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473985</v>
+        <v>473832</v>
       </c>
       <c r="R13" t="n">
-        <v>7071183</v>
+        <v>7071225</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,11 +1905,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1919,10 +1931,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120257874</v>
+        <v>120257863</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,21 +1947,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>474185</v>
+        <v>473881</v>
       </c>
       <c r="R14" t="n">
-        <v>7071205</v>
+        <v>7071306</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,6 +2007,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,10 +2038,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120257882</v>
+        <v>120257871</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>91023</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2033,25 +2050,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2078,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474249</v>
+        <v>474203</v>
       </c>
       <c r="R15" t="n">
-        <v>7071213</v>
+        <v>7071251</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,11 +2114,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,10 +2140,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120257876</v>
+        <v>120257884</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2156,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2180,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473697</v>
+        <v>473879</v>
       </c>
       <c r="R16" t="n">
-        <v>7071274</v>
+        <v>7071280</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2230,10 +2242,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120257866</v>
+        <v>120257861</v>
       </c>
       <c r="B17" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,16 +2258,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2270,10 +2282,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473843</v>
+        <v>473749</v>
       </c>
       <c r="R17" t="n">
-        <v>7071272</v>
+        <v>7071315</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2310,7 +2322,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2337,7 +2349,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120257858</v>
+        <v>120257859</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2377,10 +2389,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473697</v>
+        <v>473696</v>
       </c>
       <c r="R18" t="n">
-        <v>7071295</v>
+        <v>7071310</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2417,7 +2429,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2444,7 +2456,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120257851</v>
+        <v>120257849</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2484,10 +2496,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473805</v>
+        <v>474289</v>
       </c>
       <c r="R19" t="n">
-        <v>7071239</v>
+        <v>7071246</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2524,7 +2536,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2551,10 +2563,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120257883</v>
+        <v>120257846</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2567,21 +2579,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2591,10 +2603,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>474185</v>
+        <v>473799</v>
       </c>
       <c r="R20" t="n">
-        <v>7071226</v>
+        <v>7071305</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2627,11 +2639,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2658,10 +2665,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120257877</v>
+        <v>120257866</v>
       </c>
       <c r="B21" t="n">
-        <v>79623</v>
+        <v>57336</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2674,21 +2681,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2698,10 +2705,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473888</v>
+        <v>473843</v>
       </c>
       <c r="R21" t="n">
-        <v>7071263</v>
+        <v>7071272</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,6 +2741,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2760,10 +2772,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120257878</v>
+        <v>120257874</v>
       </c>
       <c r="B22" t="n">
-        <v>57341</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2772,50 +2784,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100110</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Margitbränna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473745</v>
+        <v>474185</v>
       </c>
       <c r="R22" t="n">
-        <v>7071314</v>
+        <v>7071205</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120257860</v>
+        <v>120257876</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2890,21 +2890,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473734</v>
+        <v>473697</v>
       </c>
       <c r="R23" t="n">
-        <v>7071302</v>
+        <v>7071274</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2950,11 +2950,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2981,10 +2976,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120257867</v>
+        <v>120257870</v>
       </c>
       <c r="B24" t="n">
-        <v>57336</v>
+        <v>79624</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2997,21 +2992,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3021,10 +3016,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473747</v>
+        <v>473888</v>
       </c>
       <c r="R24" t="n">
-        <v>7071278</v>
+        <v>7071263</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3057,11 +3052,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3088,10 +3078,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120257863</v>
+        <v>120257886</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>86895</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3104,21 +3094,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3128,10 +3118,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473881</v>
+        <v>473784</v>
       </c>
       <c r="R25" t="n">
-        <v>7071306</v>
+        <v>7071287</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3164,11 +3154,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3195,10 +3180,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120257865</v>
+        <v>120257883</v>
       </c>
       <c r="B26" t="n">
-        <v>90527</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3211,21 +3196,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3235,10 +3220,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473741</v>
+        <v>474185</v>
       </c>
       <c r="R26" t="n">
-        <v>7071312</v>
+        <v>7071226</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3271,6 +3256,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3297,10 +3287,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120257853</v>
+        <v>120257882</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3313,21 +3303,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3337,10 +3327,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473789</v>
+        <v>474249</v>
       </c>
       <c r="R27" t="n">
-        <v>7071287</v>
+        <v>7071213</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3377,7 +3367,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3404,10 +3394,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120257846</v>
+        <v>120257865</v>
       </c>
       <c r="B28" t="n">
-        <v>90580</v>
+        <v>90527</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3420,21 +3410,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3444,10 +3434,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473799</v>
+        <v>473741</v>
       </c>
       <c r="R28" t="n">
-        <v>7071305</v>
+        <v>7071312</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3506,10 +3496,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120257842</v>
+        <v>120257860</v>
       </c>
       <c r="B29" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3522,21 +3512,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3546,10 +3536,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474194</v>
+        <v>473734</v>
       </c>
       <c r="R29" t="n">
-        <v>7071238</v>
+        <v>7071302</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3582,6 +3572,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3608,7 +3603,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120257859</v>
+        <v>120257853</v>
       </c>
       <c r="B30" t="n">
         <v>57320</v>
@@ -3648,10 +3643,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473696</v>
+        <v>473789</v>
       </c>
       <c r="R30" t="n">
-        <v>7071310</v>
+        <v>7071287</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3688,7 +3683,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3715,10 +3710,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120257861</v>
+        <v>120257868</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3731,16 +3726,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3755,10 +3750,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473749</v>
+        <v>473985</v>
       </c>
       <c r="R31" t="n">
-        <v>7071315</v>
+        <v>7071183</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3795,7 +3790,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3822,10 +3817,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120257854</v>
+        <v>120257867</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3838,16 +3833,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3862,10 +3857,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473715</v>
+        <v>473747</v>
       </c>
       <c r="R32" t="n">
-        <v>7071284</v>
+        <v>7071278</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3902,7 +3897,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3929,10 +3924,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120257845</v>
+        <v>120257858</v>
       </c>
       <c r="B33" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3945,21 +3940,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3969,7 +3964,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473701</v>
+        <v>473697</v>
       </c>
       <c r="R33" t="n">
         <v>7071295</v>
@@ -4005,6 +4000,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4031,10 +4031,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120257871</v>
+        <v>120257852</v>
       </c>
       <c r="B34" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4043,25 +4043,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474203</v>
+        <v>473757</v>
       </c>
       <c r="R34" t="n">
-        <v>7071251</v>
+        <v>7071281</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4107,6 +4107,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4133,10 +4138,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120257852</v>
+        <v>120257880</v>
       </c>
       <c r="B35" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4149,21 +4154,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4173,10 +4178,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473757</v>
+        <v>473769</v>
       </c>
       <c r="R35" t="n">
-        <v>7071281</v>
+        <v>7071290</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4209,11 +4214,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 14097-2024 artfynd.xlsx
+++ b/artfynd/A 14097-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120257842</v>
+        <v>120257881</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474194</v>
+        <v>473819</v>
       </c>
       <c r="R2" t="n">
-        <v>7071238</v>
+        <v>7071302</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120257881</v>
+        <v>120257851</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473819</v>
+        <v>473805</v>
       </c>
       <c r="R3" t="n">
-        <v>7071302</v>
+        <v>7071239</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120257851</v>
+        <v>120257856</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473805</v>
+        <v>473708</v>
       </c>
       <c r="R4" t="n">
-        <v>7071239</v>
+        <v>7071283</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120257877</v>
+        <v>120257880</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>90598</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473888</v>
+        <v>473769</v>
       </c>
       <c r="R5" t="n">
-        <v>7071263</v>
+        <v>7071290</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120257854</v>
+        <v>120257886</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>86895</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473715</v>
+        <v>473784</v>
       </c>
       <c r="R6" t="n">
-        <v>7071284</v>
+        <v>7071287</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120257845</v>
+        <v>120257854</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473701</v>
+        <v>473715</v>
       </c>
       <c r="R7" t="n">
-        <v>7071295</v>
+        <v>7071284</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120257844</v>
+        <v>120257865</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>90527</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473793</v>
+        <v>473741</v>
       </c>
       <c r="R8" t="n">
-        <v>7071278</v>
+        <v>7071312</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120257862</v>
+        <v>120257853</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473877</v>
+        <v>473789</v>
       </c>
       <c r="R9" t="n">
-        <v>7071316</v>
+        <v>7071287</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,7 +1484,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120257885</v>
+        <v>120257861</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473867</v>
+        <v>473749</v>
       </c>
       <c r="R10" t="n">
-        <v>7071321</v>
+        <v>7071315</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,6 +1587,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120257878</v>
+        <v>120257852</v>
       </c>
       <c r="B11" t="n">
-        <v>57341</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,50 +1630,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100110</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Margitbränna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473745</v>
+        <v>473757</v>
       </c>
       <c r="R11" t="n">
-        <v>7071314</v>
+        <v>7071281</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,6 +1694,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1722,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120257856</v>
+        <v>120257867</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1738,16 +1741,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1762,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473708</v>
+        <v>473747</v>
       </c>
       <c r="R12" t="n">
-        <v>7071283</v>
+        <v>7071278</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,7 +1805,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1829,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120257875</v>
+        <v>120257882</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1845,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1869,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473832</v>
+        <v>474249</v>
       </c>
       <c r="R13" t="n">
-        <v>7071225</v>
+        <v>7071213</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,6 +1908,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1931,7 +1939,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120257863</v>
+        <v>120257860</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1971,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473881</v>
+        <v>473734</v>
       </c>
       <c r="R14" t="n">
-        <v>7071306</v>
+        <v>7071302</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,7 +2019,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2038,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120257871</v>
+        <v>120257862</v>
       </c>
       <c r="B15" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2050,25 +2058,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2078,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>474203</v>
+        <v>473877</v>
       </c>
       <c r="R15" t="n">
-        <v>7071251</v>
+        <v>7071316</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2114,6 +2122,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2140,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120257884</v>
+        <v>120257883</v>
       </c>
       <c r="B16" t="n">
         <v>78542</v>
@@ -2180,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473879</v>
+        <v>474185</v>
       </c>
       <c r="R16" t="n">
-        <v>7071280</v>
+        <v>7071226</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2216,6 +2229,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2242,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120257861</v>
+        <v>120257876</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2258,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2282,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473749</v>
+        <v>473697</v>
       </c>
       <c r="R17" t="n">
-        <v>7071315</v>
+        <v>7071274</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2318,11 +2336,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2349,10 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120257859</v>
+        <v>120257846</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2365,21 +2378,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2389,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473696</v>
+        <v>473799</v>
       </c>
       <c r="R18" t="n">
-        <v>7071310</v>
+        <v>7071305</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2425,11 +2438,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2456,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120257849</v>
+        <v>120257868</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2472,16 +2480,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2496,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>474289</v>
+        <v>473985</v>
       </c>
       <c r="R19" t="n">
-        <v>7071246</v>
+        <v>7071183</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2536,7 +2544,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2563,7 +2571,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120257846</v>
+        <v>120257845</v>
       </c>
       <c r="B20" t="n">
         <v>90580</v>
@@ -2603,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473799</v>
+        <v>473701</v>
       </c>
       <c r="R20" t="n">
-        <v>7071305</v>
+        <v>7071295</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2665,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120257866</v>
+        <v>120257885</v>
       </c>
       <c r="B21" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2681,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2705,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473843</v>
+        <v>473867</v>
       </c>
       <c r="R21" t="n">
-        <v>7071272</v>
+        <v>7071321</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2741,11 +2749,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2772,7 +2775,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120257874</v>
+        <v>120257877</v>
       </c>
       <c r="B22" t="n">
         <v>79623</v>
@@ -2812,10 +2815,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>474185</v>
+        <v>473888</v>
       </c>
       <c r="R22" t="n">
-        <v>7071205</v>
+        <v>7071263</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2874,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120257876</v>
+        <v>120257878</v>
       </c>
       <c r="B23" t="n">
-        <v>79623</v>
+        <v>57341</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2886,38 +2889,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100110</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Margitbränna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473697</v>
+        <v>473745</v>
       </c>
       <c r="R23" t="n">
-        <v>7071274</v>
+        <v>7071314</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3078,10 +3093,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120257886</v>
+        <v>120257874</v>
       </c>
       <c r="B25" t="n">
-        <v>86895</v>
+        <v>79623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3094,21 +3109,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3118,10 +3133,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473784</v>
+        <v>474185</v>
       </c>
       <c r="R25" t="n">
-        <v>7071287</v>
+        <v>7071205</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3180,10 +3195,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120257883</v>
+        <v>120257858</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3196,21 +3211,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3220,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>474185</v>
+        <v>473697</v>
       </c>
       <c r="R26" t="n">
-        <v>7071226</v>
+        <v>7071295</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3260,7 +3275,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3287,7 +3302,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120257882</v>
+        <v>120257884</v>
       </c>
       <c r="B27" t="n">
         <v>78542</v>
@@ -3327,10 +3342,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>474249</v>
+        <v>473879</v>
       </c>
       <c r="R27" t="n">
-        <v>7071213</v>
+        <v>7071280</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3363,11 +3378,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3394,10 +3404,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120257865</v>
+        <v>120257844</v>
       </c>
       <c r="B28" t="n">
-        <v>90527</v>
+        <v>90580</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3410,21 +3420,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3434,10 +3444,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473741</v>
+        <v>473793</v>
       </c>
       <c r="R28" t="n">
-        <v>7071312</v>
+        <v>7071278</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3496,10 +3506,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120257860</v>
+        <v>120257871</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3508,25 +3518,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3536,10 +3546,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473734</v>
+        <v>474203</v>
       </c>
       <c r="R29" t="n">
-        <v>7071302</v>
+        <v>7071251</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3572,11 +3582,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3603,7 +3608,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120257853</v>
+        <v>120257849</v>
       </c>
       <c r="B30" t="n">
         <v>57320</v>
@@ -3643,10 +3648,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473789</v>
+        <v>474289</v>
       </c>
       <c r="R30" t="n">
-        <v>7071287</v>
+        <v>7071246</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3683,7 +3688,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3710,7 +3715,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120257868</v>
+        <v>120257866</v>
       </c>
       <c r="B31" t="n">
         <v>57336</v>
@@ -3750,10 +3755,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473985</v>
+        <v>473843</v>
       </c>
       <c r="R31" t="n">
-        <v>7071183</v>
+        <v>7071272</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3817,10 +3822,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120257867</v>
+        <v>120257875</v>
       </c>
       <c r="B32" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3833,21 +3838,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3857,10 +3862,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473747</v>
+        <v>473832</v>
       </c>
       <c r="R32" t="n">
-        <v>7071278</v>
+        <v>7071225</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3893,11 +3898,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3924,7 +3924,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120257858</v>
+        <v>120257863</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473697</v>
+        <v>473881</v>
       </c>
       <c r="R33" t="n">
-        <v>7071295</v>
+        <v>7071306</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4031,10 +4031,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120257852</v>
+        <v>120257842</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4047,21 +4047,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473757</v>
+        <v>474194</v>
       </c>
       <c r="R34" t="n">
-        <v>7071281</v>
+        <v>7071238</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4107,11 +4107,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4138,10 +4133,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120257880</v>
+        <v>120257859</v>
       </c>
       <c r="B35" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4154,21 +4149,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4178,10 +4173,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473769</v>
+        <v>473696</v>
       </c>
       <c r="R35" t="n">
-        <v>7071290</v>
+        <v>7071310</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4214,6 +4209,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 14097-2024 artfynd.xlsx
+++ b/artfynd/A 14097-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120257881</v>
+        <v>120257856</v>
       </c>
       <c r="B2" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473819</v>
+        <v>473708</v>
       </c>
       <c r="R2" t="n">
-        <v>7071302</v>
+        <v>7071283</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120257851</v>
+        <v>120257883</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473805</v>
+        <v>474185</v>
       </c>
       <c r="R3" t="n">
-        <v>7071239</v>
+        <v>7071226</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120257856</v>
+        <v>120257861</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473708</v>
+        <v>473749</v>
       </c>
       <c r="R4" t="n">
-        <v>7071283</v>
+        <v>7071315</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120257880</v>
+        <v>120257854</v>
       </c>
       <c r="B5" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473769</v>
+        <v>473715</v>
       </c>
       <c r="R5" t="n">
-        <v>7071290</v>
+        <v>7071284</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120257886</v>
+        <v>120257852</v>
       </c>
       <c r="B6" t="n">
-        <v>86895</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473784</v>
+        <v>473757</v>
       </c>
       <c r="R6" t="n">
-        <v>7071287</v>
+        <v>7071281</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120257854</v>
+        <v>120257870</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473715</v>
+        <v>473888</v>
       </c>
       <c r="R7" t="n">
-        <v>7071284</v>
+        <v>7071263</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120257865</v>
+        <v>120257842</v>
       </c>
       <c r="B8" t="n">
-        <v>90527</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473741</v>
+        <v>474194</v>
       </c>
       <c r="R8" t="n">
-        <v>7071312</v>
+        <v>7071238</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120257853</v>
+        <v>120257858</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1444,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473789</v>
+        <v>473697</v>
       </c>
       <c r="R9" t="n">
-        <v>7071287</v>
+        <v>7071295</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120257861</v>
+        <v>120257881</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473749</v>
+        <v>473819</v>
       </c>
       <c r="R10" t="n">
-        <v>7071315</v>
+        <v>7071302</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120257852</v>
+        <v>120257867</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,16 +1639,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1658,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473757</v>
+        <v>473747</v>
       </c>
       <c r="R11" t="n">
-        <v>7071281</v>
+        <v>7071278</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1703,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120257867</v>
+        <v>120257845</v>
       </c>
       <c r="B12" t="n">
-        <v>57336</v>
+        <v>90580</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473747</v>
+        <v>473701</v>
       </c>
       <c r="R12" t="n">
-        <v>7071278</v>
+        <v>7071295</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,11 +1806,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,7 +1832,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120257882</v>
+        <v>120257884</v>
       </c>
       <c r="B13" t="n">
         <v>78542</v>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>474249</v>
+        <v>473879</v>
       </c>
       <c r="R13" t="n">
-        <v>7071213</v>
+        <v>7071280</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,11 +1908,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,7 +1934,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120257860</v>
+        <v>120257851</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -1979,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473734</v>
+        <v>473805</v>
       </c>
       <c r="R14" t="n">
-        <v>7071302</v>
+        <v>7071239</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2014,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,7 +2041,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120257862</v>
+        <v>120257860</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2086,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473877</v>
+        <v>473734</v>
       </c>
       <c r="R15" t="n">
-        <v>7071316</v>
+        <v>7071302</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2121,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120257883</v>
+        <v>120257846</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,21 +2164,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>474185</v>
+        <v>473799</v>
       </c>
       <c r="R16" t="n">
-        <v>7071226</v>
+        <v>7071305</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,11 +2224,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,7 +2250,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120257876</v>
+        <v>120257874</v>
       </c>
       <c r="B17" t="n">
         <v>79623</v>
@@ -2300,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473697</v>
+        <v>474185</v>
       </c>
       <c r="R17" t="n">
-        <v>7071274</v>
+        <v>7071205</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2362,10 +2352,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120257846</v>
+        <v>120257878</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>57341</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2374,38 +2364,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100110</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Margitbränna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473799</v>
+        <v>473745</v>
       </c>
       <c r="R18" t="n">
-        <v>7071305</v>
+        <v>7071314</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2464,10 +2466,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120257868</v>
+        <v>120257885</v>
       </c>
       <c r="B19" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2480,21 +2482,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2506,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473985</v>
+        <v>473867</v>
       </c>
       <c r="R19" t="n">
-        <v>7071183</v>
+        <v>7071321</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,11 +2542,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,10 +2568,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120257845</v>
+        <v>120257853</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,21 +2584,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2611,10 +2608,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473701</v>
+        <v>473789</v>
       </c>
       <c r="R20" t="n">
-        <v>7071295</v>
+        <v>7071287</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2647,6 +2644,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2673,10 +2675,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120257885</v>
+        <v>120257844</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2689,21 +2691,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2715,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473867</v>
+        <v>473793</v>
       </c>
       <c r="R21" t="n">
-        <v>7071321</v>
+        <v>7071278</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2775,10 +2777,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120257877</v>
+        <v>120257886</v>
       </c>
       <c r="B22" t="n">
-        <v>79623</v>
+        <v>86895</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2791,21 +2793,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2815,10 +2817,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473888</v>
+        <v>473784</v>
       </c>
       <c r="R22" t="n">
-        <v>7071263</v>
+        <v>7071287</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,10 +2879,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120257878</v>
+        <v>120257882</v>
       </c>
       <c r="B23" t="n">
-        <v>57341</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2889,50 +2891,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100110</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Margitbränna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473745</v>
+        <v>474249</v>
       </c>
       <c r="R23" t="n">
-        <v>7071314</v>
+        <v>7071213</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2965,6 +2955,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2991,10 +2986,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120257870</v>
+        <v>120257863</v>
       </c>
       <c r="B24" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3007,21 +3002,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3031,10 +3026,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473888</v>
+        <v>473881</v>
       </c>
       <c r="R24" t="n">
-        <v>7071263</v>
+        <v>7071306</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3067,6 +3062,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3093,10 +3093,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120257874</v>
+        <v>120257866</v>
       </c>
       <c r="B25" t="n">
-        <v>79623</v>
+        <v>57336</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3109,21 +3109,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>474185</v>
+        <v>473843</v>
       </c>
       <c r="R25" t="n">
-        <v>7071205</v>
+        <v>7071272</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3169,6 +3169,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3195,10 +3200,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120257858</v>
+        <v>120257880</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3211,21 +3216,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3235,10 +3240,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473697</v>
+        <v>473769</v>
       </c>
       <c r="R26" t="n">
-        <v>7071295</v>
+        <v>7071290</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3271,11 +3276,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3302,10 +3302,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120257884</v>
+        <v>120257877</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3318,21 +3318,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3342,10 +3342,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473879</v>
+        <v>473888</v>
       </c>
       <c r="R27" t="n">
-        <v>7071280</v>
+        <v>7071263</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3404,10 +3404,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120257844</v>
+        <v>120257871</v>
       </c>
       <c r="B28" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3416,25 +3416,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473793</v>
+        <v>474203</v>
       </c>
       <c r="R28" t="n">
-        <v>7071278</v>
+        <v>7071251</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3506,10 +3506,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120257871</v>
+        <v>120257865</v>
       </c>
       <c r="B29" t="n">
-        <v>91023</v>
+        <v>90527</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3518,25 +3518,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>112</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>474203</v>
+        <v>473741</v>
       </c>
       <c r="R29" t="n">
-        <v>7071251</v>
+        <v>7071312</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3608,10 +3608,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120257849</v>
+        <v>120257875</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3624,21 +3624,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>474289</v>
+        <v>473832</v>
       </c>
       <c r="R30" t="n">
-        <v>7071246</v>
+        <v>7071225</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3684,11 +3684,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3715,10 +3710,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120257866</v>
+        <v>120257849</v>
       </c>
       <c r="B31" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3731,16 +3726,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3755,10 +3750,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473843</v>
+        <v>474289</v>
       </c>
       <c r="R31" t="n">
-        <v>7071272</v>
+        <v>7071246</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3795,7 +3790,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3822,10 +3817,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120257875</v>
+        <v>120257868</v>
       </c>
       <c r="B32" t="n">
-        <v>79623</v>
+        <v>57336</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3838,21 +3833,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3862,10 +3857,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473832</v>
+        <v>473985</v>
       </c>
       <c r="R32" t="n">
-        <v>7071225</v>
+        <v>7071183</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3898,6 +3893,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3924,7 +3924,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120257863</v>
+        <v>120257862</v>
       </c>
       <c r="B33" t="n">
         <v>57320</v>
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473881</v>
+        <v>473877</v>
       </c>
       <c r="R33" t="n">
-        <v>7071306</v>
+        <v>7071316</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4031,10 +4031,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120257842</v>
+        <v>120257859</v>
       </c>
       <c r="B34" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4047,21 +4047,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>474194</v>
+        <v>473696</v>
       </c>
       <c r="R34" t="n">
-        <v>7071238</v>
+        <v>7071310</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4107,6 +4107,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4133,10 +4138,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120257859</v>
+        <v>120257876</v>
       </c>
       <c r="B35" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4149,21 +4154,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4173,10 +4178,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473696</v>
+        <v>473697</v>
       </c>
       <c r="R35" t="n">
-        <v>7071310</v>
+        <v>7071274</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4209,11 +4214,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 14097-2024 artfynd.xlsx
+++ b/artfynd/A 14097-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120257856</v>
+        <v>120257883</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473708</v>
+        <v>474185</v>
       </c>
       <c r="R2" t="n">
-        <v>7071283</v>
+        <v>7071226</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120257883</v>
+        <v>120257856</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474185</v>
+        <v>473708</v>
       </c>
       <c r="R3" t="n">
-        <v>7071226</v>
+        <v>7071283</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120257870</v>
+        <v>120257858</v>
       </c>
       <c r="B7" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473888</v>
+        <v>473697</v>
       </c>
       <c r="R7" t="n">
-        <v>7071263</v>
+        <v>7071295</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120257858</v>
+        <v>120257870</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473697</v>
+        <v>473888</v>
       </c>
       <c r="R9" t="n">
-        <v>7071295</v>
+        <v>7071263</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1495,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120257881</v>
+        <v>120257867</v>
       </c>
       <c r="B10" t="n">
-        <v>90598</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473819</v>
+        <v>473747</v>
       </c>
       <c r="R10" t="n">
-        <v>7071302</v>
+        <v>7071278</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1597,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120257867</v>
+        <v>120257881</v>
       </c>
       <c r="B11" t="n">
-        <v>57336</v>
+        <v>90598</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473747</v>
+        <v>473819</v>
       </c>
       <c r="R11" t="n">
-        <v>7071278</v>
+        <v>7071302</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
